--- a/automatizacion/registro_licitaciones.xlsx
+++ b/automatizacion/registro_licitaciones.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instrucciones" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Licitaciones" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Listas" sheetId="3" state="hidden" r:id="rId3"/>
+    <sheet name="Instrucciones" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Licitaciones" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Listas" sheetId="3" state="hidden" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Licitaciones'!$A$5:$AG$8</definedName>
@@ -23,7 +23,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="DD/MM/YYYY"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -73,8 +73,13 @@
       <b val="1"/>
       <sz val="11"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <sz val="9"/>
+    </font>
   </fonts>
-  <fills count="9">
+  <fills count="12">
     <fill>
       <patternFill/>
     </fill>
@@ -116,6 +121,21 @@
         <fgColor rgb="00EDEDED"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC7CE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00A9D08E"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -143,7 +163,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="77">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -198,6 +218,59 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -564,7 +637,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:A23"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="120" customWidth="1" min="1" max="1"/>
   </cols>
@@ -726,7 +799,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:AG1005"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
     <col width="9" customWidth="1" min="2" max="2"/>
@@ -1032,7 +1105,7 @@
       </c>
       <c r="C6" s="17" t="inlineStr">
         <is>
-          <t>TL-LYC-CM-001</t>
+          <t>TL-LYC-CM-101</t>
         </is>
       </c>
       <c r="D6" s="18" t="inlineStr">
@@ -1040,13 +1113,13 @@
           <t>Sí</t>
         </is>
       </c>
-      <c r="E6" s="19" t="inlineStr"/>
+      <c r="E6" s="19" t="n"/>
       <c r="F6" s="20" t="n">
         <v>365</v>
       </c>
       <c r="G6" s="20" t="inlineStr">
         <is>
-          <t>CTR-CM-001</t>
+          <t>CTR-CM-101</t>
         </is>
       </c>
       <c r="H6" s="20" t="inlineStr">
@@ -1056,7 +1129,7 @@
       </c>
       <c r="I6" s="20" t="inlineStr">
         <is>
-          <t>1500.50</t>
+          <t>1250.00</t>
         </is>
       </c>
       <c r="J6" s="20" t="inlineStr">
@@ -1066,22 +1139,22 @@
       </c>
       <c r="K6" s="20" t="inlineStr">
         <is>
-          <t>20100000001</t>
+          <t>20100000101</t>
         </is>
       </c>
       <c r="L6" s="20" t="inlineStr">
         <is>
-          <t>Empresa contratante de prueba 001 SAC</t>
+          <t>Empresa contratante de prueba 101 SAC</t>
         </is>
       </c>
       <c r="M6" s="20" t="inlineStr">
         <is>
-          <t>Servicio licitado de prueba (IF)</t>
+          <t>Servicio licitado de prueba (AC)</t>
         </is>
       </c>
       <c r="N6" s="20" t="inlineStr">
         <is>
-          <t>Atributos de la tarifa de prueba 001</t>
+          <t>Atributos de la tarifa de prueba 101</t>
         </is>
       </c>
       <c r="O6" s="20" t="inlineStr">
@@ -1089,55 +1162,71 @@
           <t>Lima Metropolitana</t>
         </is>
       </c>
-      <c r="P6" s="20" t="inlineStr"/>
+      <c r="P6" s="20" t="n"/>
       <c r="Q6" s="18" t="inlineStr">
         <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="R6" s="20" t="inlineStr">
+        <is>
+          <t>Detalle de arrendamiento de circuitos para la tarifa 101</t>
+        </is>
+      </c>
+      <c r="S6" s="18" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="R6" s="20" t="inlineStr"/>
-      <c r="S6" s="18" t="inlineStr">
+      <c r="T6" s="20" t="n"/>
+      <c r="U6" s="18" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="T6" s="20" t="inlineStr"/>
-      <c r="U6" s="18" t="inlineStr">
+      <c r="V6" s="20" t="n"/>
+      <c r="W6" s="18" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="V6" s="20" t="inlineStr"/>
-      <c r="W6" s="18" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="X6" s="20" t="inlineStr">
-        <is>
-          <t>Detalle de internet fijo para la tarifa 001</t>
-        </is>
-      </c>
+      <c r="X6" s="20" t="n"/>
       <c r="Y6" s="18" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z6" s="20" t="inlineStr"/>
+      <c r="Z6" s="20" t="n"/>
       <c r="AA6" s="18" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="AB6" s="20" t="inlineStr"/>
+      <c r="AB6" s="20" t="n"/>
       <c r="AC6" s="21">
         <f>IF(C6="","",(Q6="Sí")+(S6="Sí")+(U6="Sí")+(W6="Sí")+(Y6="Sí")+(AA6="Sí"))</f>
         <v/>
       </c>
-      <c r="AD6" s="22" t="n"/>
-      <c r="AE6" s="22" t="n"/>
-      <c r="AF6" s="22" t="n"/>
-      <c r="AG6" s="22" t="n"/>
+      <c r="AD6" s="33" t="inlineStr">
+        <is>
+          <t>Registro definitivo</t>
+        </is>
+      </c>
+      <c r="AE6" s="25" t="inlineStr">
+        <is>
+          <t>26796</t>
+        </is>
+      </c>
+      <c r="AF6" s="25" t="inlineStr">
+        <is>
+          <t>2026-10-20 12:22:40</t>
+        </is>
+      </c>
+      <c r="AG6" s="25" t="inlineStr">
+        <is>
+          <t>duración 365 días | registro definitivo OK</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="16" t="n">
@@ -1150,7 +1239,7 @@
       </c>
       <c r="C7" s="17" t="inlineStr">
         <is>
-          <t>TL-LYC-CM-002</t>
+          <t>TL-LYC-CM-102</t>
         </is>
       </c>
       <c r="D7" s="18" t="inlineStr">
@@ -1158,13 +1247,13 @@
           <t>Sí</t>
         </is>
       </c>
-      <c r="E7" s="19" t="inlineStr"/>
+      <c r="E7" s="19" t="n"/>
       <c r="F7" s="20" t="n">
         <v>365</v>
       </c>
       <c r="G7" s="20" t="inlineStr">
         <is>
-          <t>CTR-CM-002</t>
+          <t>CTR-CM-102</t>
         </is>
       </c>
       <c r="H7" s="20" t="inlineStr">
@@ -1174,7 +1263,7 @@
       </c>
       <c r="I7" s="20" t="inlineStr">
         <is>
-          <t>3250.75</t>
+          <t>1251.00</t>
         </is>
       </c>
       <c r="J7" s="20" t="inlineStr">
@@ -1184,22 +1273,22 @@
       </c>
       <c r="K7" s="20" t="inlineStr">
         <is>
-          <t>20100000002</t>
+          <t>20100000102</t>
         </is>
       </c>
       <c r="L7" s="20" t="inlineStr">
         <is>
-          <t>Empresa contratante de prueba 002 SAC</t>
+          <t>Empresa contratante de prueba 102 SAC</t>
         </is>
       </c>
       <c r="M7" s="20" t="inlineStr">
         <is>
-          <t>Servicio licitado de prueba (TVP+SM+TF)</t>
+          <t>Servicio licitado de prueba (OS)</t>
         </is>
       </c>
       <c r="N7" s="20" t="inlineStr">
         <is>
-          <t>Atributos de la tarifa de prueba 002</t>
+          <t>Atributos de la tarifa de prueba 102</t>
         </is>
       </c>
       <c r="O7" s="20" t="inlineStr">
@@ -1207,63 +1296,75 @@
           <t>Lima Metropolitana</t>
         </is>
       </c>
-      <c r="P7" s="20" t="inlineStr"/>
+      <c r="P7" s="20" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="Q7" s="18" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="R7" s="20" t="inlineStr"/>
+      <c r="R7" s="20" t="n"/>
       <c r="S7" s="18" t="inlineStr">
         <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="T7" s="20" t="inlineStr">
+        <is>
+          <t>Detalle de otros servicios para la tarifa 102</t>
+        </is>
+      </c>
+      <c r="U7" s="18" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="T7" s="20" t="inlineStr"/>
-      <c r="U7" s="18" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="V7" s="20" t="inlineStr">
-        <is>
-          <t>Detalle de televisión de paga para la tarifa 002</t>
-        </is>
-      </c>
+      <c r="V7" s="20" t="n"/>
       <c r="W7" s="18" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X7" s="20" t="inlineStr"/>
+      <c r="X7" s="20" t="n"/>
       <c r="Y7" s="18" t="inlineStr">
         <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="Z7" s="20" t="inlineStr">
-        <is>
-          <t>Detalle de servicio móvil para la tarifa 002</t>
-        </is>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Z7" s="20" t="n"/>
       <c r="AA7" s="18" t="inlineStr">
         <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="AB7" s="20" t="inlineStr">
-        <is>
-          <t>Detalle de telefonía fija para la tarifa 002</t>
-        </is>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AB7" s="20" t="n"/>
       <c r="AC7" s="21">
         <f>IF(C7="","",(Q7="Sí")+(S7="Sí")+(U7="Sí")+(W7="Sí")+(Y7="Sí")+(AA7="Sí"))</f>
         <v/>
       </c>
-      <c r="AD7" s="22" t="n"/>
-      <c r="AE7" s="22" t="n"/>
-      <c r="AF7" s="22" t="n"/>
-      <c r="AG7" s="22" t="n"/>
+      <c r="AD7" s="33" t="inlineStr">
+        <is>
+          <t>Registro definitivo</t>
+        </is>
+      </c>
+      <c r="AE7" s="25" t="inlineStr">
+        <is>
+          <t>26798</t>
+        </is>
+      </c>
+      <c r="AF7" s="25" t="inlineStr">
+        <is>
+          <t>2026-10-20 12:38:34</t>
+        </is>
+      </c>
+      <c r="AG7" s="25" t="inlineStr">
+        <is>
+          <t>duración 365 días | registro definitivo OK</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="16" t="n">
@@ -1276,7 +1377,7 @@
       </c>
       <c r="C8" s="17" t="inlineStr">
         <is>
-          <t>TL-LYC-CM-003</t>
+          <t>TL-LYC-CM-103</t>
         </is>
       </c>
       <c r="D8" s="18" t="inlineStr">
@@ -1284,13 +1385,13 @@
           <t>Sí</t>
         </is>
       </c>
-      <c r="E8" s="19" t="inlineStr"/>
+      <c r="E8" s="19" t="n"/>
       <c r="F8" s="20" t="n">
         <v>365</v>
       </c>
       <c r="G8" s="20" t="inlineStr">
         <is>
-          <t>CTR-CM-003</t>
+          <t>CTR-CM-103</t>
         </is>
       </c>
       <c r="H8" s="20" t="inlineStr">
@@ -1300,7 +1401,7 @@
       </c>
       <c r="I8" s="20" t="inlineStr">
         <is>
-          <t>9800</t>
+          <t>1252.00</t>
         </is>
       </c>
       <c r="J8" s="20" t="inlineStr">
@@ -1310,22 +1411,22 @@
       </c>
       <c r="K8" s="20" t="inlineStr">
         <is>
-          <t>20100000003</t>
+          <t>20100000103</t>
         </is>
       </c>
       <c r="L8" s="20" t="inlineStr">
         <is>
-          <t>Empresa contratante de prueba 003 SAC</t>
+          <t>Empresa contratante de prueba 103 SAC</t>
         </is>
       </c>
       <c r="M8" s="20" t="inlineStr">
         <is>
-          <t>Servicio licitado de prueba (AC+OS+TVP+IF+SM+TF)</t>
+          <t>Servicio licitado de prueba (TVP)</t>
         </is>
       </c>
       <c r="N8" s="20" t="inlineStr">
         <is>
-          <t>Atributos de la tarifa de prueba 003</t>
+          <t>Atributos de la tarifa de prueba 103</t>
         </is>
       </c>
       <c r="O8" s="20" t="inlineStr">
@@ -1333,31 +1434,19 @@
           <t>Lima Metropolitana</t>
         </is>
       </c>
-      <c r="P8" s="20" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+      <c r="P8" s="20" t="n"/>
       <c r="Q8" s="18" t="inlineStr">
         <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="R8" s="20" t="inlineStr">
-        <is>
-          <t>Detalle de arrendamiento de circuitos para la tarifa 003</t>
-        </is>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R8" s="20" t="n"/>
       <c r="S8" s="18" t="inlineStr">
         <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="T8" s="20" t="inlineStr">
-        <is>
-          <t>Detalle de otros servicios para la tarifa 003</t>
-        </is>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="T8" s="20" t="n"/>
       <c r="U8" s="18" t="inlineStr">
         <is>
           <t>Sí</t>
@@ -1365,361 +1454,6510 @@
       </c>
       <c r="V8" s="20" t="inlineStr">
         <is>
-          <t>Detalle de televisión de paga para la tarifa 003</t>
+          <t>Detalle de televisión de paga para la tarifa 103</t>
         </is>
       </c>
       <c r="W8" s="18" t="inlineStr">
         <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="X8" s="20" t="inlineStr">
-        <is>
-          <t>Detalle de internet fijo para la tarifa 003</t>
-        </is>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X8" s="20" t="n"/>
       <c r="Y8" s="18" t="inlineStr">
         <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="Z8" s="20" t="inlineStr">
-        <is>
-          <t>Detalle de servicio móvil para la tarifa 003</t>
-        </is>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Z8" s="20" t="n"/>
       <c r="AA8" s="18" t="inlineStr">
         <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="AB8" s="20" t="inlineStr">
-        <is>
-          <t>Detalle de telefonía fija para la tarifa 003</t>
-        </is>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AB8" s="20" t="n"/>
       <c r="AC8" s="21">
         <f>IF(C8="","",(Q8="Sí")+(S8="Sí")+(U8="Sí")+(W8="Sí")+(Y8="Sí")+(AA8="Sí"))</f>
         <v/>
       </c>
-      <c r="AD8" s="22" t="n"/>
-      <c r="AE8" s="22" t="n"/>
-      <c r="AF8" s="22" t="n"/>
-      <c r="AG8" s="22" t="n"/>
+      <c r="AD8" s="33" t="inlineStr">
+        <is>
+          <t>Registro definitivo</t>
+        </is>
+      </c>
+      <c r="AE8" s="25" t="inlineStr">
+        <is>
+          <t>26799</t>
+        </is>
+      </c>
+      <c r="AF8" s="25" t="inlineStr">
+        <is>
+          <t>2026-10-20 12:38:48</t>
+        </is>
+      </c>
+      <c r="AG8" s="25" t="inlineStr">
+        <is>
+          <t>duración 365 días | registro definitivo OK</t>
+        </is>
+      </c>
     </row>
     <row r="9">
+      <c r="A9" t="n">
+        <v>4</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>TL-LYC-CM-104</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
       <c r="E9" s="23" t="n"/>
+      <c r="F9" t="n">
+        <v>365</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>CTR-CM-104</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1253.00</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Soles</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>20100000104</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>Empresa contratante de prueba 104 SAC</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>Servicio licitado de prueba (IF)</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>Atributos de la tarifa de prueba 104</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>Lima Metropolitana</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>Detalle de internet fijo para la tarifa 104</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="AC9" s="21">
         <f>IF(C9="","",(Q9="Sí")+(S9="Sí")+(U9="Sí")+(W9="Sí")+(Y9="Sí")+(AA9="Sí"))</f>
         <v/>
       </c>
+      <c r="AD9" s="68" t="inlineStr">
+        <is>
+          <t>Registro definitivo</t>
+        </is>
+      </c>
+      <c r="AE9" s="2" t="inlineStr">
+        <is>
+          <t>26800</t>
+        </is>
+      </c>
+      <c r="AF9" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20 12:39:01</t>
+        </is>
+      </c>
+      <c r="AG9" s="2" t="inlineStr">
+        <is>
+          <t>duración 365 días | registro definitivo OK</t>
+        </is>
+      </c>
     </row>
     <row r="10">
+      <c r="A10" t="n">
+        <v>5</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>TL-LYC-CM-105</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
       <c r="E10" s="23" t="n"/>
+      <c r="F10" t="n">
+        <v>365</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>CTR-CM-105</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Público</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1254.00</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Dolares</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>20100000105</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>Empresa contratante de prueba 105 SAC</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>Servicio licitado de prueba (SM)</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>Atributos de la tarifa de prueba 105</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>Lima Metropolitana</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>Detalle de servicio móvil para la tarifa 105</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="AC10" s="21">
         <f>IF(C10="","",(Q10="Sí")+(S10="Sí")+(U10="Sí")+(W10="Sí")+(Y10="Sí")+(AA10="Sí"))</f>
         <v/>
       </c>
+      <c r="AD10" s="68" t="inlineStr">
+        <is>
+          <t>Registro definitivo</t>
+        </is>
+      </c>
+      <c r="AE10" s="2" t="inlineStr">
+        <is>
+          <t>26801</t>
+        </is>
+      </c>
+      <c r="AF10" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20 12:39:15</t>
+        </is>
+      </c>
+      <c r="AG10" s="2" t="inlineStr">
+        <is>
+          <t>duración 365 días | registro definitivo OK</t>
+        </is>
+      </c>
     </row>
     <row r="11">
+      <c r="A11" t="n">
+        <v>6</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>TL-LYC-CM-106</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
       <c r="E11" s="23" t="n"/>
+      <c r="F11" t="n">
+        <v>365</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>CTR-CM-106</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1255.00</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Euro</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>20100000106</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>Empresa contratante de prueba 106 SAC</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>Servicio licitado de prueba (TF)</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>Atributos de la tarifa de prueba 106</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>Lima Metropolitana</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>Detalle de telefonía fija para la tarifa 106</t>
+        </is>
+      </c>
       <c r="AC11" s="21">
         <f>IF(C11="","",(Q11="Sí")+(S11="Sí")+(U11="Sí")+(W11="Sí")+(Y11="Sí")+(AA11="Sí"))</f>
         <v/>
       </c>
+      <c r="AD11" s="68" t="inlineStr">
+        <is>
+          <t>Registro definitivo</t>
+        </is>
+      </c>
+      <c r="AE11" s="2" t="inlineStr">
+        <is>
+          <t>26802</t>
+        </is>
+      </c>
+      <c r="AF11" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20 12:39:28</t>
+        </is>
+      </c>
+      <c r="AG11" s="2" t="inlineStr">
+        <is>
+          <t>duración 365 días | registro definitivo OK</t>
+        </is>
+      </c>
     </row>
     <row r="12">
+      <c r="A12" t="n">
+        <v>7</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>TL-LYC-CM-107</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
       <c r="E12" s="23" t="n"/>
+      <c r="F12" t="n">
+        <v>365</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>CTR-CM-107</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Público</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1756.00</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Soles</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>20100000107</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>Empresa contratante de prueba 107 SAC</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>Servicio licitado de prueba (AC+OS+TVP)</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>Atributos de la tarifa de prueba 107</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>Lima Metropolitana</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>Detalle de arrendamiento de circuitos para la tarifa 107</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Detalle de otros servicios para la tarifa 107</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Detalle de televisión de paga para la tarifa 107</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="AC12" s="21">
         <f>IF(C12="","",(Q12="Sí")+(S12="Sí")+(U12="Sí")+(W12="Sí")+(Y12="Sí")+(AA12="Sí"))</f>
         <v/>
       </c>
+      <c r="AD12" s="68" t="inlineStr">
+        <is>
+          <t>Registro definitivo</t>
+        </is>
+      </c>
+      <c r="AE12" s="2" t="inlineStr">
+        <is>
+          <t>26797</t>
+        </is>
+      </c>
+      <c r="AF12" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20 12:23:52</t>
+        </is>
+      </c>
+      <c r="AG12" s="2" t="inlineStr">
+        <is>
+          <t>duración 365 días | registro definitivo OK</t>
+        </is>
+      </c>
     </row>
     <row r="13">
+      <c r="A13" t="n">
+        <v>8</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>TL-LYC-CM-108</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
       <c r="E13" s="23" t="n"/>
+      <c r="F13" t="n">
+        <v>365</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>CTR-CM-108</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1757.00</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Dolares</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>20100000108</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>Empresa contratante de prueba 108 SAC</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>Servicio licitado de prueba (AC+OS+IF)</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>Atributos de la tarifa de prueba 108</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>Lima Metropolitana</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>Detalle de arrendamiento de circuitos para la tarifa 108</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Detalle de otros servicios para la tarifa 108</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>Detalle de internet fijo para la tarifa 108</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="AC13" s="21">
         <f>IF(C13="","",(Q13="Sí")+(S13="Sí")+(U13="Sí")+(W13="Sí")+(Y13="Sí")+(AA13="Sí"))</f>
         <v/>
       </c>
+      <c r="AD13" s="68" t="inlineStr">
+        <is>
+          <t>Registro definitivo</t>
+        </is>
+      </c>
+      <c r="AE13" s="2" t="inlineStr">
+        <is>
+          <t>26803</t>
+        </is>
+      </c>
+      <c r="AF13" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20 12:39:42</t>
+        </is>
+      </c>
+      <c r="AG13" s="2" t="inlineStr">
+        <is>
+          <t>duración 365 días | registro definitivo OK</t>
+        </is>
+      </c>
     </row>
     <row r="14">
+      <c r="A14" t="n">
+        <v>9</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>TL-LYC-CM-109</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
       <c r="E14" s="23" t="n"/>
+      <c r="F14" t="n">
+        <v>365</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>CTR-CM-109</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Público</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1758.00</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Euro</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>20100000109</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>Empresa contratante de prueba 109 SAC</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>Servicio licitado de prueba (AC+OS+SM)</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>Atributos de la tarifa de prueba 109</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>Lima Metropolitana</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>Detalle de arrendamiento de circuitos para la tarifa 109</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Detalle de otros servicios para la tarifa 109</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>Detalle de servicio móvil para la tarifa 109</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="AC14" s="21">
         <f>IF(C14="","",(Q14="Sí")+(S14="Sí")+(U14="Sí")+(W14="Sí")+(Y14="Sí")+(AA14="Sí"))</f>
         <v/>
       </c>
+      <c r="AD14" s="68" t="inlineStr">
+        <is>
+          <t>Registro definitivo</t>
+        </is>
+      </c>
+      <c r="AE14" s="2" t="inlineStr">
+        <is>
+          <t>26804</t>
+        </is>
+      </c>
+      <c r="AF14" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20 12:39:56</t>
+        </is>
+      </c>
+      <c r="AG14" s="2" t="inlineStr">
+        <is>
+          <t>duración 365 días | registro definitivo OK</t>
+        </is>
+      </c>
     </row>
     <row r="15">
+      <c r="A15" t="n">
+        <v>10</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>TL-LYC-CM-110</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
       <c r="E15" s="23" t="n"/>
+      <c r="F15" t="n">
+        <v>365</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>CTR-CM-110</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1759.00</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Soles</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>20100000110</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>Empresa contratante de prueba 110 SAC</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>Servicio licitado de prueba (AC+OS+TF)</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>Atributos de la tarifa de prueba 110</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>Lima Metropolitana</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>Detalle de arrendamiento de circuitos para la tarifa 110</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Detalle de otros servicios para la tarifa 110</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>Detalle de telefonía fija para la tarifa 110</t>
+        </is>
+      </c>
       <c r="AC15" s="21">
         <f>IF(C15="","",(Q15="Sí")+(S15="Sí")+(U15="Sí")+(W15="Sí")+(Y15="Sí")+(AA15="Sí"))</f>
         <v/>
       </c>
+      <c r="AD15" s="68" t="inlineStr">
+        <is>
+          <t>Registro definitivo</t>
+        </is>
+      </c>
+      <c r="AE15" s="2" t="inlineStr">
+        <is>
+          <t>26805</t>
+        </is>
+      </c>
+      <c r="AF15" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20 12:40:09</t>
+        </is>
+      </c>
+      <c r="AG15" s="2" t="inlineStr">
+        <is>
+          <t>duración 365 días | registro definitivo OK</t>
+        </is>
+      </c>
     </row>
     <row r="16">
+      <c r="A16" t="n">
+        <v>11</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>TL-LYC-CM-111</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
       <c r="E16" s="23" t="n"/>
+      <c r="F16" t="n">
+        <v>365</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>CTR-CM-111</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Público</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1760.00</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Dolares</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>20100000111</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>Empresa contratante de prueba 111 SAC</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>Servicio licitado de prueba (AC+TVP+IF)</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>Atributos de la tarifa de prueba 111</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>Lima Metropolitana</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>Detalle de arrendamiento de circuitos para la tarifa 111</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Detalle de televisión de paga para la tarifa 111</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>Detalle de internet fijo para la tarifa 111</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="AC16" s="21">
         <f>IF(C16="","",(Q16="Sí")+(S16="Sí")+(U16="Sí")+(W16="Sí")+(Y16="Sí")+(AA16="Sí"))</f>
         <v/>
       </c>
+      <c r="AD16" s="68" t="inlineStr">
+        <is>
+          <t>Registro definitivo</t>
+        </is>
+      </c>
+      <c r="AE16" s="2" t="inlineStr">
+        <is>
+          <t>26806</t>
+        </is>
+      </c>
+      <c r="AF16" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20 12:40:23</t>
+        </is>
+      </c>
+      <c r="AG16" s="2" t="inlineStr">
+        <is>
+          <t>duración 365 días | registro definitivo OK</t>
+        </is>
+      </c>
     </row>
     <row r="17">
+      <c r="A17" t="n">
+        <v>12</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>TL-LYC-CM-112</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
       <c r="E17" s="23" t="n"/>
+      <c r="F17" t="n">
+        <v>365</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>CTR-CM-112</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1761.00</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Euro</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>20100000112</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>Empresa contratante de prueba 112 SAC</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>Servicio licitado de prueba (AC+TVP+SM)</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>Atributos de la tarifa de prueba 112</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>Lima Metropolitana</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>Detalle de arrendamiento de circuitos para la tarifa 112</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Detalle de televisión de paga para la tarifa 112</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>Detalle de servicio móvil para la tarifa 112</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="AC17" s="21">
         <f>IF(C17="","",(Q17="Sí")+(S17="Sí")+(U17="Sí")+(W17="Sí")+(Y17="Sí")+(AA17="Sí"))</f>
         <v/>
       </c>
+      <c r="AD17" s="68" t="inlineStr">
+        <is>
+          <t>Registro definitivo</t>
+        </is>
+      </c>
+      <c r="AE17" s="2" t="inlineStr">
+        <is>
+          <t>26807</t>
+        </is>
+      </c>
+      <c r="AF17" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20 12:40:36</t>
+        </is>
+      </c>
+      <c r="AG17" s="2" t="inlineStr">
+        <is>
+          <t>duración 365 días | registro definitivo OK</t>
+        </is>
+      </c>
     </row>
     <row r="18">
+      <c r="A18" t="n">
+        <v>13</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>TL-LYC-CM-113</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
       <c r="E18" s="23" t="n"/>
+      <c r="F18" t="n">
+        <v>365</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>CTR-CM-113</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Público</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1762.00</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Soles</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>20100000113</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>Empresa contratante de prueba 113 SAC</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>Servicio licitado de prueba (AC+TVP+TF)</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>Atributos de la tarifa de prueba 113</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>Lima Metropolitana</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>Detalle de arrendamiento de circuitos para la tarifa 113</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Detalle de televisión de paga para la tarifa 113</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>Detalle de telefonía fija para la tarifa 113</t>
+        </is>
+      </c>
       <c r="AC18" s="21">
         <f>IF(C18="","",(Q18="Sí")+(S18="Sí")+(U18="Sí")+(W18="Sí")+(Y18="Sí")+(AA18="Sí"))</f>
         <v/>
       </c>
+      <c r="AD18" s="68" t="inlineStr">
+        <is>
+          <t>Registro definitivo</t>
+        </is>
+      </c>
+      <c r="AE18" s="2" t="inlineStr">
+        <is>
+          <t>26808</t>
+        </is>
+      </c>
+      <c r="AF18" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20 12:40:50</t>
+        </is>
+      </c>
+      <c r="AG18" s="2" t="inlineStr">
+        <is>
+          <t>duración 365 días | registro definitivo OK</t>
+        </is>
+      </c>
     </row>
     <row r="19">
+      <c r="A19" t="n">
+        <v>14</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>TL-LYC-CM-114</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
       <c r="E19" s="23" t="n"/>
+      <c r="F19" t="n">
+        <v>365</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>CTR-CM-114</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1763.00</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Dolares</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>20100000114</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>Empresa contratante de prueba 114 SAC</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>Servicio licitado de prueba (AC+IF+SM)</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>Atributos de la tarifa de prueba 114</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>Lima Metropolitana</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>Detalle de arrendamiento de circuitos para la tarifa 114</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>Detalle de internet fijo para la tarifa 114</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>Detalle de servicio móvil para la tarifa 114</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="AC19" s="21">
         <f>IF(C19="","",(Q19="Sí")+(S19="Sí")+(U19="Sí")+(W19="Sí")+(Y19="Sí")+(AA19="Sí"))</f>
         <v/>
       </c>
+      <c r="AD19" s="68" t="inlineStr">
+        <is>
+          <t>Registro definitivo</t>
+        </is>
+      </c>
+      <c r="AE19" s="2" t="inlineStr">
+        <is>
+          <t>26809</t>
+        </is>
+      </c>
+      <c r="AF19" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20 12:41:03</t>
+        </is>
+      </c>
+      <c r="AG19" s="2" t="inlineStr">
+        <is>
+          <t>duración 365 días | registro definitivo OK</t>
+        </is>
+      </c>
     </row>
     <row r="20">
+      <c r="A20" t="n">
+        <v>15</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>TL-LYC-CM-115</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
       <c r="E20" s="23" t="n"/>
+      <c r="F20" t="n">
+        <v>365</v>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>CTR-CM-115</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Público</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1764.00</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Euro</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>20100000115</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>Empresa contratante de prueba 115 SAC</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>Servicio licitado de prueba (AC+IF+TF)</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>Atributos de la tarifa de prueba 115</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>Lima Metropolitana</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>Detalle de arrendamiento de circuitos para la tarifa 115</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>Detalle de internet fijo para la tarifa 115</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>Detalle de telefonía fija para la tarifa 115</t>
+        </is>
+      </c>
       <c r="AC20" s="21">
         <f>IF(C20="","",(Q20="Sí")+(S20="Sí")+(U20="Sí")+(W20="Sí")+(Y20="Sí")+(AA20="Sí"))</f>
         <v/>
       </c>
+      <c r="AD20" s="68" t="inlineStr">
+        <is>
+          <t>Registro definitivo</t>
+        </is>
+      </c>
+      <c r="AE20" s="2" t="inlineStr">
+        <is>
+          <t>26810</t>
+        </is>
+      </c>
+      <c r="AF20" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20 12:41:17</t>
+        </is>
+      </c>
+      <c r="AG20" s="2" t="inlineStr">
+        <is>
+          <t>duración 365 días | registro definitivo OK</t>
+        </is>
+      </c>
     </row>
     <row r="21">
+      <c r="A21" t="n">
+        <v>16</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>TL-LYC-CM-116</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
       <c r="E21" s="23" t="n"/>
+      <c r="F21" t="n">
+        <v>365</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>CTR-CM-116</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1765.00</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Soles</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>20100000116</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>Empresa contratante de prueba 116 SAC</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>Servicio licitado de prueba (AC+SM+TF)</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>Atributos de la tarifa de prueba 116</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>Lima Metropolitana</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>Detalle de arrendamiento de circuitos para la tarifa 116</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>Detalle de servicio móvil para la tarifa 116</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>Detalle de telefonía fija para la tarifa 116</t>
+        </is>
+      </c>
       <c r="AC21" s="21">
         <f>IF(C21="","",(Q21="Sí")+(S21="Sí")+(U21="Sí")+(W21="Sí")+(Y21="Sí")+(AA21="Sí"))</f>
         <v/>
       </c>
+      <c r="AD21" s="68" t="inlineStr">
+        <is>
+          <t>Registro definitivo</t>
+        </is>
+      </c>
+      <c r="AE21" s="2" t="inlineStr">
+        <is>
+          <t>26811</t>
+        </is>
+      </c>
+      <c r="AF21" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20 12:41:30</t>
+        </is>
+      </c>
+      <c r="AG21" s="2" t="inlineStr">
+        <is>
+          <t>duración 365 días | registro definitivo OK</t>
+        </is>
+      </c>
     </row>
     <row r="22">
+      <c r="A22" t="n">
+        <v>17</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>TL-LYC-CM-117</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
       <c r="E22" s="23" t="n"/>
+      <c r="F22" t="n">
+        <v>365</v>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>CTR-CM-117</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Público</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1766.00</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Dolares</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>20100000117</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>Empresa contratante de prueba 117 SAC</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>Servicio licitado de prueba (OS+TVP+IF)</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>Atributos de la tarifa de prueba 117</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>Lima Metropolitana</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Detalle de otros servicios para la tarifa 117</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Detalle de televisión de paga para la tarifa 117</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>Detalle de internet fijo para la tarifa 117</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="AC22" s="21">
         <f>IF(C22="","",(Q22="Sí")+(S22="Sí")+(U22="Sí")+(W22="Sí")+(Y22="Sí")+(AA22="Sí"))</f>
         <v/>
       </c>
+      <c r="AD22" s="68" t="inlineStr">
+        <is>
+          <t>Registro definitivo</t>
+        </is>
+      </c>
+      <c r="AE22" s="2" t="inlineStr">
+        <is>
+          <t>26812</t>
+        </is>
+      </c>
+      <c r="AF22" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20 12:41:44</t>
+        </is>
+      </c>
+      <c r="AG22" s="2" t="inlineStr">
+        <is>
+          <t>duración 365 días | registro definitivo OK</t>
+        </is>
+      </c>
     </row>
     <row r="23">
+      <c r="A23" t="n">
+        <v>18</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>TL-LYC-CM-118</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
       <c r="E23" s="23" t="n"/>
+      <c r="F23" t="n">
+        <v>365</v>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>CTR-CM-118</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1767.00</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Euro</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>20100000118</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>Empresa contratante de prueba 118 SAC</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>Servicio licitado de prueba (OS+TVP+SM)</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>Atributos de la tarifa de prueba 118</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>Lima Metropolitana</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Detalle de otros servicios para la tarifa 118</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Detalle de televisión de paga para la tarifa 118</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>Detalle de servicio móvil para la tarifa 118</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="AC23" s="21">
         <f>IF(C23="","",(Q23="Sí")+(S23="Sí")+(U23="Sí")+(W23="Sí")+(Y23="Sí")+(AA23="Sí"))</f>
         <v/>
       </c>
+      <c r="AD23" s="68" t="inlineStr">
+        <is>
+          <t>Registro definitivo</t>
+        </is>
+      </c>
+      <c r="AE23" s="2" t="inlineStr">
+        <is>
+          <t>26813</t>
+        </is>
+      </c>
+      <c r="AF23" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20 12:41:57</t>
+        </is>
+      </c>
+      <c r="AG23" s="2" t="inlineStr">
+        <is>
+          <t>duración 365 días | registro definitivo OK</t>
+        </is>
+      </c>
     </row>
     <row r="24">
+      <c r="A24" t="n">
+        <v>19</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>TL-LYC-CM-119</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
       <c r="E24" s="23" t="n"/>
+      <c r="F24" t="n">
+        <v>365</v>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>CTR-CM-119</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Público</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1768.00</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Soles</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>20100000119</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>Empresa contratante de prueba 119 SAC</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>Servicio licitado de prueba (OS+TVP+TF)</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>Atributos de la tarifa de prueba 119</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>Lima Metropolitana</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Detalle de otros servicios para la tarifa 119</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Detalle de televisión de paga para la tarifa 119</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>Detalle de telefonía fija para la tarifa 119</t>
+        </is>
+      </c>
       <c r="AC24" s="21">
         <f>IF(C24="","",(Q24="Sí")+(S24="Sí")+(U24="Sí")+(W24="Sí")+(Y24="Sí")+(AA24="Sí"))</f>
         <v/>
       </c>
+      <c r="AD24" s="68" t="inlineStr">
+        <is>
+          <t>Registro definitivo</t>
+        </is>
+      </c>
+      <c r="AE24" s="2" t="inlineStr">
+        <is>
+          <t>26814</t>
+        </is>
+      </c>
+      <c r="AF24" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20 12:42:11</t>
+        </is>
+      </c>
+      <c r="AG24" s="2" t="inlineStr">
+        <is>
+          <t>duración 365 días | registro definitivo OK</t>
+        </is>
+      </c>
     </row>
     <row r="25">
+      <c r="A25" t="n">
+        <v>20</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>TL-LYC-CM-120</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
       <c r="E25" s="23" t="n"/>
+      <c r="F25" t="n">
+        <v>365</v>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>CTR-CM-120</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1769.00</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>Dolares</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>20100000120</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>Empresa contratante de prueba 120 SAC</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>Servicio licitado de prueba (OS+IF+SM)</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>Atributos de la tarifa de prueba 120</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>Lima Metropolitana</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Detalle de otros servicios para la tarifa 120</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>Detalle de internet fijo para la tarifa 120</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>Detalle de servicio móvil para la tarifa 120</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="AC25" s="21">
         <f>IF(C25="","",(Q25="Sí")+(S25="Sí")+(U25="Sí")+(W25="Sí")+(Y25="Sí")+(AA25="Sí"))</f>
         <v/>
       </c>
+      <c r="AD25" s="68" t="inlineStr">
+        <is>
+          <t>Registro definitivo</t>
+        </is>
+      </c>
+      <c r="AE25" s="2" t="inlineStr">
+        <is>
+          <t>26815</t>
+        </is>
+      </c>
+      <c r="AF25" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20 12:42:24</t>
+        </is>
+      </c>
+      <c r="AG25" s="2" t="inlineStr">
+        <is>
+          <t>duración 365 días | registro definitivo OK</t>
+        </is>
+      </c>
     </row>
     <row r="26">
+      <c r="A26" t="n">
+        <v>21</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>TL-LYC-CM-121</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
       <c r="E26" s="23" t="n"/>
+      <c r="F26" t="n">
+        <v>365</v>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>CTR-CM-121</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Público</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1770.00</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>Euro</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>20100000121</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>Empresa contratante de prueba 121 SAC</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>Servicio licitado de prueba (OS+IF+TF)</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>Atributos de la tarifa de prueba 121</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>Lima Metropolitana</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Detalle de otros servicios para la tarifa 121</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>Detalle de internet fijo para la tarifa 121</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>Detalle de telefonía fija para la tarifa 121</t>
+        </is>
+      </c>
       <c r="AC26" s="21">
         <f>IF(C26="","",(Q26="Sí")+(S26="Sí")+(U26="Sí")+(W26="Sí")+(Y26="Sí")+(AA26="Sí"))</f>
         <v/>
       </c>
+      <c r="AD26" s="68" t="inlineStr">
+        <is>
+          <t>Registro definitivo</t>
+        </is>
+      </c>
+      <c r="AE26" s="2" t="inlineStr">
+        <is>
+          <t>26816</t>
+        </is>
+      </c>
+      <c r="AF26" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20 12:42:38</t>
+        </is>
+      </c>
+      <c r="AG26" s="2" t="inlineStr">
+        <is>
+          <t>duración 365 días | registro definitivo OK</t>
+        </is>
+      </c>
     </row>
     <row r="27">
+      <c r="A27" t="n">
+        <v>22</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>TL-LYC-CM-122</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
       <c r="E27" s="23" t="n"/>
+      <c r="F27" t="n">
+        <v>365</v>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>CTR-CM-122</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1771.00</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>Soles</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>20100000122</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>Empresa contratante de prueba 122 SAC</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>Servicio licitado de prueba (OS+SM+TF)</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>Atributos de la tarifa de prueba 122</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>Lima Metropolitana</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Detalle de otros servicios para la tarifa 122</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>Detalle de servicio móvil para la tarifa 122</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>Detalle de telefonía fija para la tarifa 122</t>
+        </is>
+      </c>
       <c r="AC27" s="21">
         <f>IF(C27="","",(Q27="Sí")+(S27="Sí")+(U27="Sí")+(W27="Sí")+(Y27="Sí")+(AA27="Sí"))</f>
         <v/>
       </c>
+      <c r="AD27" s="68" t="inlineStr">
+        <is>
+          <t>Registro definitivo</t>
+        </is>
+      </c>
+      <c r="AE27" s="2" t="inlineStr">
+        <is>
+          <t>26817</t>
+        </is>
+      </c>
+      <c r="AF27" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20 12:42:52</t>
+        </is>
+      </c>
+      <c r="AG27" s="2" t="inlineStr">
+        <is>
+          <t>duración 365 días | registro definitivo OK</t>
+        </is>
+      </c>
     </row>
     <row r="28">
+      <c r="A28" t="n">
+        <v>23</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>TL-LYC-CM-123</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
       <c r="E28" s="23" t="n"/>
+      <c r="F28" t="n">
+        <v>365</v>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>CTR-CM-123</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Público</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>1772.00</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>Dolares</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>20100000123</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>Empresa contratante de prueba 123 SAC</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>Servicio licitado de prueba (TVP+IF+SM)</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>Atributos de la tarifa de prueba 123</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>Lima Metropolitana</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Detalle de televisión de paga para la tarifa 123</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>Detalle de internet fijo para la tarifa 123</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>Detalle de servicio móvil para la tarifa 123</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="AC28" s="21">
         <f>IF(C28="","",(Q28="Sí")+(S28="Sí")+(U28="Sí")+(W28="Sí")+(Y28="Sí")+(AA28="Sí"))</f>
         <v/>
       </c>
+      <c r="AD28" s="68" t="inlineStr">
+        <is>
+          <t>Registro definitivo</t>
+        </is>
+      </c>
+      <c r="AE28" s="2" t="inlineStr">
+        <is>
+          <t>26844</t>
+        </is>
+      </c>
+      <c r="AF28" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20 14:06:26</t>
+        </is>
+      </c>
+      <c r="AG28" s="2" t="inlineStr">
+        <is>
+          <t>duración 365 días | registro definitivo OK</t>
+        </is>
+      </c>
     </row>
     <row r="29">
+      <c r="A29" t="n">
+        <v>24</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>TL-LYC-CM-124</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
       <c r="E29" s="23" t="n"/>
+      <c r="F29" t="n">
+        <v>365</v>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>CTR-CM-124</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>1773.00</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>Euro</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>20100000124</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>Empresa contratante de prueba 124 SAC</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>Servicio licitado de prueba (TVP+IF+TF)</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>Atributos de la tarifa de prueba 124</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>Lima Metropolitana</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Detalle de televisión de paga para la tarifa 124</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>Detalle de internet fijo para la tarifa 124</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>Detalle de telefonía fija para la tarifa 124</t>
+        </is>
+      </c>
       <c r="AC29" s="21">
         <f>IF(C29="","",(Q29="Sí")+(S29="Sí")+(U29="Sí")+(W29="Sí")+(Y29="Sí")+(AA29="Sí"))</f>
         <v/>
       </c>
+      <c r="AD29" s="68" t="inlineStr">
+        <is>
+          <t>Registro definitivo</t>
+        </is>
+      </c>
+      <c r="AE29" s="2" t="inlineStr">
+        <is>
+          <t>26819</t>
+        </is>
+      </c>
+      <c r="AF29" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20 12:43:05</t>
+        </is>
+      </c>
+      <c r="AG29" s="2" t="inlineStr">
+        <is>
+          <t>duración 365 días | registro definitivo OK</t>
+        </is>
+      </c>
     </row>
     <row r="30">
+      <c r="A30" t="n">
+        <v>25</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>TL-LYC-CM-125</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
       <c r="E30" s="23" t="n"/>
+      <c r="F30" t="n">
+        <v>365</v>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>CTR-CM-125</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Público</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>1774.00</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>Soles</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>20100000125</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>Empresa contratante de prueba 125 SAC</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>Servicio licitado de prueba (TVP+SM+TF)</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>Atributos de la tarifa de prueba 125</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>Lima Metropolitana</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Detalle de televisión de paga para la tarifa 125</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>Detalle de servicio móvil para la tarifa 125</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>Detalle de telefonía fija para la tarifa 125</t>
+        </is>
+      </c>
       <c r="AC30" s="21">
         <f>IF(C30="","",(Q30="Sí")+(S30="Sí")+(U30="Sí")+(W30="Sí")+(Y30="Sí")+(AA30="Sí"))</f>
         <v/>
       </c>
+      <c r="AD30" s="68" t="inlineStr">
+        <is>
+          <t>Registro definitivo</t>
+        </is>
+      </c>
+      <c r="AE30" s="2" t="inlineStr">
+        <is>
+          <t>26845</t>
+        </is>
+      </c>
+      <c r="AF30" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20 14:06:40</t>
+        </is>
+      </c>
+      <c r="AG30" s="2" t="inlineStr">
+        <is>
+          <t>duración 365 días | registro definitivo OK</t>
+        </is>
+      </c>
     </row>
     <row r="31">
+      <c r="A31" t="n">
+        <v>26</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>TL-LYC-CM-126</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
       <c r="E31" s="23" t="n"/>
+      <c r="F31" t="n">
+        <v>365</v>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>CTR-CM-126</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>1775.00</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>Dolares</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>20100000126</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>Empresa contratante de prueba 126 SAC</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>Servicio licitado de prueba (IF+SM+TF)</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>Atributos de la tarifa de prueba 126</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>Lima Metropolitana</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>Detalle de internet fijo para la tarifa 126</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>Detalle de servicio móvil para la tarifa 126</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>Detalle de telefonía fija para la tarifa 126</t>
+        </is>
+      </c>
       <c r="AC31" s="21">
         <f>IF(C31="","",(Q31="Sí")+(S31="Sí")+(U31="Sí")+(W31="Sí")+(Y31="Sí")+(AA31="Sí"))</f>
         <v/>
       </c>
+      <c r="AD31" s="68" t="inlineStr">
+        <is>
+          <t>Registro definitivo</t>
+        </is>
+      </c>
+      <c r="AE31" s="2" t="inlineStr">
+        <is>
+          <t>26821</t>
+        </is>
+      </c>
+      <c r="AF31" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20 12:43:19</t>
+        </is>
+      </c>
+      <c r="AG31" s="2" t="inlineStr">
+        <is>
+          <t>duración 365 días | registro definitivo OK</t>
+        </is>
+      </c>
     </row>
     <row r="32">
+      <c r="A32" t="n">
+        <v>27</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>TL-LYC-CM-127</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
       <c r="E32" s="23" t="n"/>
+      <c r="F32" t="n">
+        <v>365</v>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>CTR-CM-127</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Público</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>2026.00</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>Euro</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>20100000127</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>Empresa contratante de prueba 127 SAC</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>Servicio licitado de prueba (AC+OS+TVP+IF)</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>Atributos de la tarifa de prueba 127</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>Lima Metropolitana</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>Detalle de arrendamiento de circuitos para la tarifa 127</t>
+        </is>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Detalle de otros servicios para la tarifa 127</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Detalle de televisión de paga para la tarifa 127</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>Detalle de internet fijo para la tarifa 127</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="AC32" s="21">
         <f>IF(C32="","",(Q32="Sí")+(S32="Sí")+(U32="Sí")+(W32="Sí")+(Y32="Sí")+(AA32="Sí"))</f>
         <v/>
       </c>
+      <c r="AD32" s="68" t="inlineStr">
+        <is>
+          <t>Registro definitivo</t>
+        </is>
+      </c>
+      <c r="AE32" s="2" t="inlineStr">
+        <is>
+          <t>26822</t>
+        </is>
+      </c>
+      <c r="AF32" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20 12:43:32</t>
+        </is>
+      </c>
+      <c r="AG32" s="2" t="inlineStr">
+        <is>
+          <t>duración 365 días | registro definitivo OK</t>
+        </is>
+      </c>
     </row>
     <row r="33">
+      <c r="A33" t="n">
+        <v>28</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>TL-LYC-CM-128</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
       <c r="E33" s="23" t="n"/>
+      <c r="F33" t="n">
+        <v>365</v>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>CTR-CM-128</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>2027.00</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>Soles</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>20100000128</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>Empresa contratante de prueba 128 SAC</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>Servicio licitado de prueba (AC+OS+TVP+SM)</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>Atributos de la tarifa de prueba 128</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>Lima Metropolitana</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>Detalle de arrendamiento de circuitos para la tarifa 128</t>
+        </is>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Detalle de otros servicios para la tarifa 128</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Detalle de televisión de paga para la tarifa 128</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>Detalle de servicio móvil para la tarifa 128</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="AC33" s="21">
         <f>IF(C33="","",(Q33="Sí")+(S33="Sí")+(U33="Sí")+(W33="Sí")+(Y33="Sí")+(AA33="Sí"))</f>
         <v/>
       </c>
+      <c r="AD33" s="68" t="inlineStr">
+        <is>
+          <t>Registro definitivo</t>
+        </is>
+      </c>
+      <c r="AE33" s="2" t="inlineStr">
+        <is>
+          <t>26823</t>
+        </is>
+      </c>
+      <c r="AF33" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20 12:43:45</t>
+        </is>
+      </c>
+      <c r="AG33" s="2" t="inlineStr">
+        <is>
+          <t>duración 365 días | registro definitivo OK</t>
+        </is>
+      </c>
     </row>
     <row r="34">
+      <c r="A34" t="n">
+        <v>29</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>TL-LYC-CM-129</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
       <c r="E34" s="23" t="n"/>
+      <c r="F34" t="n">
+        <v>365</v>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>CTR-CM-129</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Público</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>2028.00</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>Dolares</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>20100000129</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>Empresa contratante de prueba 129 SAC</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>Servicio licitado de prueba (AC+OS+TVP+TF)</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>Atributos de la tarifa de prueba 129</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>Lima Metropolitana</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>Detalle de arrendamiento de circuitos para la tarifa 129</t>
+        </is>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Detalle de otros servicios para la tarifa 129</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Detalle de televisión de paga para la tarifa 129</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>Detalle de telefonía fija para la tarifa 129</t>
+        </is>
+      </c>
       <c r="AC34" s="21">
         <f>IF(C34="","",(Q34="Sí")+(S34="Sí")+(U34="Sí")+(W34="Sí")+(Y34="Sí")+(AA34="Sí"))</f>
         <v/>
       </c>
+      <c r="AD34" s="68" t="inlineStr">
+        <is>
+          <t>Registro definitivo</t>
+        </is>
+      </c>
+      <c r="AE34" s="2" t="inlineStr">
+        <is>
+          <t>26824</t>
+        </is>
+      </c>
+      <c r="AF34" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20 12:43:59</t>
+        </is>
+      </c>
+      <c r="AG34" s="2" t="inlineStr">
+        <is>
+          <t>duración 365 días | registro definitivo OK</t>
+        </is>
+      </c>
     </row>
     <row r="35">
+      <c r="A35" t="n">
+        <v>30</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>TL-LYC-CM-130</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
       <c r="E35" s="23" t="n"/>
+      <c r="F35" t="n">
+        <v>365</v>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>CTR-CM-130</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>2029.00</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>Euro</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>20100000130</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>Empresa contratante de prueba 130 SAC</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>Servicio licitado de prueba (AC+OS+IF+SM)</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>Atributos de la tarifa de prueba 130</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>Lima Metropolitana</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>Detalle de arrendamiento de circuitos para la tarifa 130</t>
+        </is>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Detalle de otros servicios para la tarifa 130</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>Detalle de internet fijo para la tarifa 130</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>Detalle de servicio móvil para la tarifa 130</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="AC35" s="21">
         <f>IF(C35="","",(Q35="Sí")+(S35="Sí")+(U35="Sí")+(W35="Sí")+(Y35="Sí")+(AA35="Sí"))</f>
         <v/>
       </c>
+      <c r="AD35" s="68" t="inlineStr">
+        <is>
+          <t>Registro definitivo</t>
+        </is>
+      </c>
+      <c r="AE35" s="2" t="inlineStr">
+        <is>
+          <t>26846</t>
+        </is>
+      </c>
+      <c r="AF35" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20 14:06:53</t>
+        </is>
+      </c>
+      <c r="AG35" s="2" t="inlineStr">
+        <is>
+          <t>duración 365 días | registro definitivo OK</t>
+        </is>
+      </c>
     </row>
     <row r="36">
+      <c r="A36" t="n">
+        <v>31</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>TL-LYC-CM-131</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
       <c r="E36" s="23" t="n"/>
+      <c r="F36" t="n">
+        <v>365</v>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>CTR-CM-131</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Público</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>2030.00</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>Soles</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>20100000131</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>Empresa contratante de prueba 131 SAC</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>Servicio licitado de prueba (AC+OS+IF+TF)</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>Atributos de la tarifa de prueba 131</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>Lima Metropolitana</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="R36" t="inlineStr">
+        <is>
+          <t>Detalle de arrendamiento de circuitos para la tarifa 131</t>
+        </is>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Detalle de otros servicios para la tarifa 131</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>Detalle de internet fijo para la tarifa 131</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>Detalle de telefonía fija para la tarifa 131</t>
+        </is>
+      </c>
       <c r="AC36" s="21">
         <f>IF(C36="","",(Q36="Sí")+(S36="Sí")+(U36="Sí")+(W36="Sí")+(Y36="Sí")+(AA36="Sí"))</f>
         <v/>
       </c>
+      <c r="AD36" s="68" t="inlineStr">
+        <is>
+          <t>Registro definitivo</t>
+        </is>
+      </c>
+      <c r="AE36" s="2" t="inlineStr">
+        <is>
+          <t>26826</t>
+        </is>
+      </c>
+      <c r="AF36" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20 12:44:12</t>
+        </is>
+      </c>
+      <c r="AG36" s="2" t="inlineStr">
+        <is>
+          <t>duración 365 días | registro definitivo OK</t>
+        </is>
+      </c>
     </row>
     <row r="37">
+      <c r="A37" t="n">
+        <v>32</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>TL-LYC-CM-132</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
       <c r="E37" s="23" t="n"/>
+      <c r="F37" t="n">
+        <v>365</v>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>CTR-CM-132</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>2031.00</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>Dolares</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>20100000132</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>Empresa contratante de prueba 132 SAC</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>Servicio licitado de prueba (AC+OS+SM+TF)</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>Atributos de la tarifa de prueba 132</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>Lima Metropolitana</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>Detalle de arrendamiento de circuitos para la tarifa 132</t>
+        </is>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Detalle de otros servicios para la tarifa 132</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>Detalle de servicio móvil para la tarifa 132</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>Detalle de telefonía fija para la tarifa 132</t>
+        </is>
+      </c>
       <c r="AC37" s="21">
         <f>IF(C37="","",(Q37="Sí")+(S37="Sí")+(U37="Sí")+(W37="Sí")+(Y37="Sí")+(AA37="Sí"))</f>
         <v/>
       </c>
+      <c r="AD37" s="68" t="inlineStr">
+        <is>
+          <t>Registro definitivo</t>
+        </is>
+      </c>
+      <c r="AE37" s="2" t="inlineStr">
+        <is>
+          <t>26827</t>
+        </is>
+      </c>
+      <c r="AF37" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20 12:44:26</t>
+        </is>
+      </c>
+      <c r="AG37" s="2" t="inlineStr">
+        <is>
+          <t>duración 365 días | registro definitivo OK</t>
+        </is>
+      </c>
     </row>
     <row r="38">
+      <c r="A38" t="n">
+        <v>33</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>TL-LYC-CM-133</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
       <c r="E38" s="23" t="n"/>
+      <c r="F38" t="n">
+        <v>365</v>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>CTR-CM-133</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Público</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>2032.00</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>Euro</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>20100000133</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>Empresa contratante de prueba 133 SAC</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>Servicio licitado de prueba (AC+TVP+IF+SM)</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>Atributos de la tarifa de prueba 133</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>Lima Metropolitana</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>Detalle de arrendamiento de circuitos para la tarifa 133</t>
+        </is>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Detalle de televisión de paga para la tarifa 133</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>Detalle de internet fijo para la tarifa 133</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>Detalle de servicio móvil para la tarifa 133</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="AC38" s="21">
         <f>IF(C38="","",(Q38="Sí")+(S38="Sí")+(U38="Sí")+(W38="Sí")+(Y38="Sí")+(AA38="Sí"))</f>
         <v/>
       </c>
+      <c r="AD38" s="68" t="inlineStr">
+        <is>
+          <t>Registro definitivo</t>
+        </is>
+      </c>
+      <c r="AE38" s="2" t="inlineStr">
+        <is>
+          <t>26828</t>
+        </is>
+      </c>
+      <c r="AF38" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20 12:44:40</t>
+        </is>
+      </c>
+      <c r="AG38" s="2" t="inlineStr">
+        <is>
+          <t>duración 365 días | registro definitivo OK</t>
+        </is>
+      </c>
     </row>
     <row r="39">
+      <c r="A39" t="n">
+        <v>34</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>TL-LYC-CM-134</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
       <c r="E39" s="23" t="n"/>
+      <c r="F39" t="n">
+        <v>365</v>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>CTR-CM-134</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>2033.00</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>Soles</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>20100000134</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>Empresa contratante de prueba 134 SAC</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>Servicio licitado de prueba (AC+TVP+IF+TF)</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>Atributos de la tarifa de prueba 134</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>Lima Metropolitana</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>Detalle de arrendamiento de circuitos para la tarifa 134</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Detalle de televisión de paga para la tarifa 134</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>Detalle de internet fijo para la tarifa 134</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>Detalle de telefonía fija para la tarifa 134</t>
+        </is>
+      </c>
       <c r="AC39" s="21">
         <f>IF(C39="","",(Q39="Sí")+(S39="Sí")+(U39="Sí")+(W39="Sí")+(Y39="Sí")+(AA39="Sí"))</f>
         <v/>
       </c>
+      <c r="AD39" s="68" t="inlineStr">
+        <is>
+          <t>Registro definitivo</t>
+        </is>
+      </c>
+      <c r="AE39" s="2" t="inlineStr">
+        <is>
+          <t>26829</t>
+        </is>
+      </c>
+      <c r="AF39" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20 12:44:53</t>
+        </is>
+      </c>
+      <c r="AG39" s="2" t="inlineStr">
+        <is>
+          <t>duración 365 días | registro definitivo OK</t>
+        </is>
+      </c>
     </row>
     <row r="40">
+      <c r="A40" t="n">
+        <v>35</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>TL-LYC-CM-135</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
       <c r="E40" s="23" t="n"/>
+      <c r="F40" t="n">
+        <v>365</v>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>CTR-CM-135</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Público</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>2034.00</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>Dolares</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>20100000135</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>Empresa contratante de prueba 135 SAC</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>Servicio licitado de prueba (AC+TVP+SM+TF)</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>Atributos de la tarifa de prueba 135</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>Lima Metropolitana</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>Detalle de arrendamiento de circuitos para la tarifa 135</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Detalle de televisión de paga para la tarifa 135</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>Detalle de servicio móvil para la tarifa 135</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>Detalle de telefonía fija para la tarifa 135</t>
+        </is>
+      </c>
       <c r="AC40" s="21">
         <f>IF(C40="","",(Q40="Sí")+(S40="Sí")+(U40="Sí")+(W40="Sí")+(Y40="Sí")+(AA40="Sí"))</f>
         <v/>
       </c>
+      <c r="AD40" s="68" t="inlineStr">
+        <is>
+          <t>Registro definitivo</t>
+        </is>
+      </c>
+      <c r="AE40" s="2" t="inlineStr">
+        <is>
+          <t>26830</t>
+        </is>
+      </c>
+      <c r="AF40" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20 12:45:06</t>
+        </is>
+      </c>
+      <c r="AG40" s="2" t="inlineStr">
+        <is>
+          <t>duración 365 días | registro definitivo OK</t>
+        </is>
+      </c>
     </row>
     <row r="41">
+      <c r="A41" t="n">
+        <v>36</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>TL-LYC-CM-136</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
       <c r="E41" s="23" t="n"/>
+      <c r="F41" t="n">
+        <v>365</v>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>CTR-CM-136</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>2035.00</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>Euro</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>20100000136</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>Empresa contratante de prueba 136 SAC</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>Servicio licitado de prueba (AC+IF+SM+TF)</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>Atributos de la tarifa de prueba 136</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>Lima Metropolitana</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>Detalle de arrendamiento de circuitos para la tarifa 136</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>Detalle de internet fijo para la tarifa 136</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>Detalle de servicio móvil para la tarifa 136</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>Detalle de telefonía fija para la tarifa 136</t>
+        </is>
+      </c>
       <c r="AC41" s="21">
         <f>IF(C41="","",(Q41="Sí")+(S41="Sí")+(U41="Sí")+(W41="Sí")+(Y41="Sí")+(AA41="Sí"))</f>
         <v/>
       </c>
+      <c r="AD41" s="68" t="inlineStr">
+        <is>
+          <t>Registro definitivo</t>
+        </is>
+      </c>
+      <c r="AE41" s="2" t="inlineStr">
+        <is>
+          <t>26831</t>
+        </is>
+      </c>
+      <c r="AF41" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20 12:45:20</t>
+        </is>
+      </c>
+      <c r="AG41" s="2" t="inlineStr">
+        <is>
+          <t>duración 365 días | registro definitivo OK</t>
+        </is>
+      </c>
     </row>
     <row r="42">
+      <c r="A42" t="n">
+        <v>37</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>TL-LYC-CM-137</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
       <c r="E42" s="23" t="n"/>
+      <c r="F42" t="n">
+        <v>365</v>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>CTR-CM-137</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Público</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>2036.00</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>Soles</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>20100000137</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>Empresa contratante de prueba 137 SAC</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>Servicio licitado de prueba (OS+TVP+IF+SM)</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>Atributos de la tarifa de prueba 137</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>Lima Metropolitana</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Detalle de otros servicios para la tarifa 137</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Detalle de televisión de paga para la tarifa 137</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>Detalle de internet fijo para la tarifa 137</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>Detalle de servicio móvil para la tarifa 137</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="AC42" s="21">
         <f>IF(C42="","",(Q42="Sí")+(S42="Sí")+(U42="Sí")+(W42="Sí")+(Y42="Sí")+(AA42="Sí"))</f>
         <v/>
       </c>
+      <c r="AD42" s="68" t="inlineStr">
+        <is>
+          <t>Registro definitivo</t>
+        </is>
+      </c>
+      <c r="AE42" s="2" t="inlineStr">
+        <is>
+          <t>26832</t>
+        </is>
+      </c>
+      <c r="AF42" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20 12:45:33</t>
+        </is>
+      </c>
+      <c r="AG42" s="2" t="inlineStr">
+        <is>
+          <t>duración 365 días | registro definitivo OK</t>
+        </is>
+      </c>
     </row>
     <row r="43">
+      <c r="A43" t="n">
+        <v>38</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>TL-LYC-CM-138</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
       <c r="E43" s="23" t="n"/>
+      <c r="F43" t="n">
+        <v>365</v>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>CTR-CM-138</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>2037.00</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>Dolares</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>20100000138</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>Empresa contratante de prueba 138 SAC</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>Servicio licitado de prueba (OS+TVP+IF+TF)</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>Atributos de la tarifa de prueba 138</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>Lima Metropolitana</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Detalle de otros servicios para la tarifa 138</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Detalle de televisión de paga para la tarifa 138</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>Detalle de internet fijo para la tarifa 138</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>Detalle de telefonía fija para la tarifa 138</t>
+        </is>
+      </c>
       <c r="AC43" s="21">
         <f>IF(C43="","",(Q43="Sí")+(S43="Sí")+(U43="Sí")+(W43="Sí")+(Y43="Sí")+(AA43="Sí"))</f>
         <v/>
       </c>
+      <c r="AD43" s="68" t="inlineStr">
+        <is>
+          <t>Registro definitivo</t>
+        </is>
+      </c>
+      <c r="AE43" s="2" t="inlineStr">
+        <is>
+          <t>26833</t>
+        </is>
+      </c>
+      <c r="AF43" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20 12:45:47</t>
+        </is>
+      </c>
+      <c r="AG43" s="2" t="inlineStr">
+        <is>
+          <t>duración 365 días | registro definitivo OK</t>
+        </is>
+      </c>
     </row>
     <row r="44">
+      <c r="A44" t="n">
+        <v>39</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>TL-LYC-CM-139</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
       <c r="E44" s="23" t="n"/>
+      <c r="F44" t="n">
+        <v>365</v>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>CTR-CM-139</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Público</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>2038.00</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>Euro</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>20100000139</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>Empresa contratante de prueba 139 SAC</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>Servicio licitado de prueba (OS+TVP+SM+TF)</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>Atributos de la tarifa de prueba 139</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>Lima Metropolitana</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Detalle de otros servicios para la tarifa 139</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Detalle de televisión de paga para la tarifa 139</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>Detalle de servicio móvil para la tarifa 139</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>Detalle de telefonía fija para la tarifa 139</t>
+        </is>
+      </c>
       <c r="AC44" s="21">
         <f>IF(C44="","",(Q44="Sí")+(S44="Sí")+(U44="Sí")+(W44="Sí")+(Y44="Sí")+(AA44="Sí"))</f>
         <v/>
       </c>
+      <c r="AD44" s="68" t="inlineStr">
+        <is>
+          <t>Registro definitivo</t>
+        </is>
+      </c>
+      <c r="AE44" s="2" t="inlineStr">
+        <is>
+          <t>26834</t>
+        </is>
+      </c>
+      <c r="AF44" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20 12:46:01</t>
+        </is>
+      </c>
+      <c r="AG44" s="2" t="inlineStr">
+        <is>
+          <t>duración 365 días | registro definitivo OK</t>
+        </is>
+      </c>
     </row>
     <row r="45">
+      <c r="A45" t="n">
+        <v>40</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>TL-LYC-CM-140</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
       <c r="E45" s="23" t="n"/>
+      <c r="F45" t="n">
+        <v>365</v>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>CTR-CM-140</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>2039.00</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>Soles</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>20100000140</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>Empresa contratante de prueba 140 SAC</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>Servicio licitado de prueba (OS+IF+SM+TF)</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>Atributos de la tarifa de prueba 140</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>Lima Metropolitana</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Detalle de otros servicios para la tarifa 140</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>Detalle de internet fijo para la tarifa 140</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>Detalle de servicio móvil para la tarifa 140</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>Detalle de telefonía fija para la tarifa 140</t>
+        </is>
+      </c>
       <c r="AC45" s="21">
         <f>IF(C45="","",(Q45="Sí")+(S45="Sí")+(U45="Sí")+(W45="Sí")+(Y45="Sí")+(AA45="Sí"))</f>
         <v/>
       </c>
+      <c r="AD45" s="68" t="inlineStr">
+        <is>
+          <t>Registro definitivo</t>
+        </is>
+      </c>
+      <c r="AE45" s="2" t="inlineStr">
+        <is>
+          <t>26835</t>
+        </is>
+      </c>
+      <c r="AF45" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20 12:46:15</t>
+        </is>
+      </c>
+      <c r="AG45" s="2" t="inlineStr">
+        <is>
+          <t>duración 365 días | registro definitivo OK</t>
+        </is>
+      </c>
     </row>
     <row r="46">
+      <c r="A46" t="n">
+        <v>41</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>TL-LYC-CM-141</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
       <c r="E46" s="23" t="n"/>
+      <c r="F46" t="n">
+        <v>365</v>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>CTR-CM-141</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Público</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>2040.00</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>Dolares</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>20100000141</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>Empresa contratante de prueba 141 SAC</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>Servicio licitado de prueba (TVP+IF+SM+TF)</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>Atributos de la tarifa de prueba 141</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>Lima Metropolitana</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Detalle de televisión de paga para la tarifa 141</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>Detalle de internet fijo para la tarifa 141</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>Detalle de servicio móvil para la tarifa 141</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>Detalle de telefonía fija para la tarifa 141</t>
+        </is>
+      </c>
       <c r="AC46" s="21">
         <f>IF(C46="","",(Q46="Sí")+(S46="Sí")+(U46="Sí")+(W46="Sí")+(Y46="Sí")+(AA46="Sí"))</f>
         <v/>
       </c>
+      <c r="AD46" s="68" t="inlineStr">
+        <is>
+          <t>Registro definitivo</t>
+        </is>
+      </c>
+      <c r="AE46" s="2" t="inlineStr">
+        <is>
+          <t>26836</t>
+        </is>
+      </c>
+      <c r="AF46" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20 12:46:28</t>
+        </is>
+      </c>
+      <c r="AG46" s="2" t="inlineStr">
+        <is>
+          <t>duración 365 días | registro definitivo OK</t>
+        </is>
+      </c>
     </row>
     <row r="47">
+      <c r="A47" t="n">
+        <v>42</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>TL-LYC-CM-142</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
       <c r="E47" s="23" t="n"/>
+      <c r="F47" t="n">
+        <v>365</v>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>CTR-CM-142</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>2291.00</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>Euro</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>20100000142</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>Empresa contratante de prueba 142 SAC</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>Servicio licitado de prueba (AC+OS+TVP+IF+SM)</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>Atributos de la tarifa de prueba 142</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>Lima Metropolitana</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="R47" t="inlineStr">
+        <is>
+          <t>Detalle de arrendamiento de circuitos para la tarifa 142</t>
+        </is>
+      </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Detalle de otros servicios para la tarifa 142</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Detalle de televisión de paga para la tarifa 142</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>Detalle de internet fijo para la tarifa 142</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>Detalle de servicio móvil para la tarifa 142</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="AC47" s="21">
         <f>IF(C47="","",(Q47="Sí")+(S47="Sí")+(U47="Sí")+(W47="Sí")+(Y47="Sí")+(AA47="Sí"))</f>
         <v/>
       </c>
+      <c r="AD47" s="68" t="inlineStr">
+        <is>
+          <t>Registro definitivo</t>
+        </is>
+      </c>
+      <c r="AE47" s="2" t="inlineStr">
+        <is>
+          <t>26847</t>
+        </is>
+      </c>
+      <c r="AF47" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20 14:07:06</t>
+        </is>
+      </c>
+      <c r="AG47" s="2" t="inlineStr">
+        <is>
+          <t>duración 365 días | registro definitivo OK</t>
+        </is>
+      </c>
     </row>
     <row r="48">
+      <c r="A48" t="n">
+        <v>43</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>TL-LYC-CM-143</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
       <c r="E48" s="23" t="n"/>
+      <c r="F48" t="n">
+        <v>365</v>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>CTR-CM-143</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Público</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>2292.00</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>Soles</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>20100000143</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>Empresa contratante de prueba 143 SAC</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>Servicio licitado de prueba (AC+OS+TVP+IF+TF)</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>Atributos de la tarifa de prueba 143</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>Lima Metropolitana</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="R48" t="inlineStr">
+        <is>
+          <t>Detalle de arrendamiento de circuitos para la tarifa 143</t>
+        </is>
+      </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Detalle de otros servicios para la tarifa 143</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Detalle de televisión de paga para la tarifa 143</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>Detalle de internet fijo para la tarifa 143</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>Detalle de telefonía fija para la tarifa 143</t>
+        </is>
+      </c>
       <c r="AC48" s="21">
         <f>IF(C48="","",(Q48="Sí")+(S48="Sí")+(U48="Sí")+(W48="Sí")+(Y48="Sí")+(AA48="Sí"))</f>
         <v/>
       </c>
+      <c r="AD48" s="68" t="inlineStr">
+        <is>
+          <t>Registro definitivo</t>
+        </is>
+      </c>
+      <c r="AE48" s="2" t="inlineStr">
+        <is>
+          <t>26838</t>
+        </is>
+      </c>
+      <c r="AF48" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20 12:46:42</t>
+        </is>
+      </c>
+      <c r="AG48" s="2" t="inlineStr">
+        <is>
+          <t>duración 365 días | registro definitivo OK</t>
+        </is>
+      </c>
     </row>
     <row r="49">
+      <c r="A49" t="n">
+        <v>44</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>TL-LYC-CM-144</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
       <c r="E49" s="23" t="n"/>
+      <c r="F49" t="n">
+        <v>365</v>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>CTR-CM-144</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>2293.00</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>Dolares</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>20100000144</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>Empresa contratante de prueba 144 SAC</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>Servicio licitado de prueba (AC+OS+TVP+SM+TF)</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>Atributos de la tarifa de prueba 144</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>Lima Metropolitana</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="R49" t="inlineStr">
+        <is>
+          <t>Detalle de arrendamiento de circuitos para la tarifa 144</t>
+        </is>
+      </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Detalle de otros servicios para la tarifa 144</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Detalle de televisión de paga para la tarifa 144</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>Detalle de servicio móvil para la tarifa 144</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>Detalle de telefonía fija para la tarifa 144</t>
+        </is>
+      </c>
       <c r="AC49" s="21">
         <f>IF(C49="","",(Q49="Sí")+(S49="Sí")+(U49="Sí")+(W49="Sí")+(Y49="Sí")+(AA49="Sí"))</f>
         <v/>
       </c>
+      <c r="AD49" s="68" t="inlineStr">
+        <is>
+          <t>Registro definitivo</t>
+        </is>
+      </c>
+      <c r="AE49" s="2" t="inlineStr">
+        <is>
+          <t>26848</t>
+        </is>
+      </c>
+      <c r="AF49" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20 14:07:20</t>
+        </is>
+      </c>
+      <c r="AG49" s="2" t="inlineStr">
+        <is>
+          <t>duración 365 días | registro definitivo OK</t>
+        </is>
+      </c>
     </row>
     <row r="50">
+      <c r="A50" t="n">
+        <v>45</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>TL-LYC-CM-145</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
       <c r="E50" s="23" t="n"/>
+      <c r="F50" t="n">
+        <v>365</v>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>CTR-CM-145</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Público</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>2294.00</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>Euro</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>20100000145</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>Empresa contratante de prueba 145 SAC</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>Servicio licitado de prueba (AC+OS+IF+SM+TF)</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>Atributos de la tarifa de prueba 145</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>Lima Metropolitana</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="R50" t="inlineStr">
+        <is>
+          <t>Detalle de arrendamiento de circuitos para la tarifa 145</t>
+        </is>
+      </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Detalle de otros servicios para la tarifa 145</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>Detalle de internet fijo para la tarifa 145</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>Detalle de servicio móvil para la tarifa 145</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>Detalle de telefonía fija para la tarifa 145</t>
+        </is>
+      </c>
       <c r="AC50" s="21">
         <f>IF(C50="","",(Q50="Sí")+(S50="Sí")+(U50="Sí")+(W50="Sí")+(Y50="Sí")+(AA50="Sí"))</f>
         <v/>
       </c>
+      <c r="AD50" s="68" t="inlineStr">
+        <is>
+          <t>Registro definitivo</t>
+        </is>
+      </c>
+      <c r="AE50" s="2" t="inlineStr">
+        <is>
+          <t>26840</t>
+        </is>
+      </c>
+      <c r="AF50" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20 12:46:55</t>
+        </is>
+      </c>
+      <c r="AG50" s="2" t="inlineStr">
+        <is>
+          <t>duración 365 días | registro definitivo OK</t>
+        </is>
+      </c>
     </row>
     <row r="51">
+      <c r="A51" t="n">
+        <v>46</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>TL-LYC-CM-146</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
       <c r="E51" s="23" t="n"/>
+      <c r="F51" t="n">
+        <v>365</v>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>CTR-CM-146</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>2295.00</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>Soles</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>20100000146</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>Empresa contratante de prueba 146 SAC</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>Servicio licitado de prueba (AC+TVP+IF+SM+TF)</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>Atributos de la tarifa de prueba 146</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>Lima Metropolitana</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="R51" t="inlineStr">
+        <is>
+          <t>Detalle de arrendamiento de circuitos para la tarifa 146</t>
+        </is>
+      </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Detalle de televisión de paga para la tarifa 146</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>Detalle de internet fijo para la tarifa 146</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>Detalle de servicio móvil para la tarifa 146</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>Detalle de telefonía fija para la tarifa 146</t>
+        </is>
+      </c>
       <c r="AC51" s="21">
         <f>IF(C51="","",(Q51="Sí")+(S51="Sí")+(U51="Sí")+(W51="Sí")+(Y51="Sí")+(AA51="Sí"))</f>
         <v/>
       </c>
+      <c r="AD51" s="68" t="inlineStr">
+        <is>
+          <t>Registro definitivo</t>
+        </is>
+      </c>
+      <c r="AE51" s="2" t="inlineStr">
+        <is>
+          <t>26849</t>
+        </is>
+      </c>
+      <c r="AF51" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20 14:07:33</t>
+        </is>
+      </c>
+      <c r="AG51" s="2" t="inlineStr">
+        <is>
+          <t>duración 365 días | registro definitivo OK</t>
+        </is>
+      </c>
     </row>
     <row r="52">
+      <c r="A52" t="n">
+        <v>47</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>TL-LYC-CM-147</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
       <c r="E52" s="23" t="n"/>
+      <c r="F52" t="n">
+        <v>365</v>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>CTR-CM-147</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Público</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>2296.00</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>Dolares</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>20100000147</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>Empresa contratante de prueba 147 SAC</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>Servicio licitado de prueba (OS+TVP+IF+SM+TF)</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>Atributos de la tarifa de prueba 147</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>Lima Metropolitana</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Detalle de otros servicios para la tarifa 147</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Detalle de televisión de paga para la tarifa 147</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>Detalle de internet fijo para la tarifa 147</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>Detalle de servicio móvil para la tarifa 147</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>Detalle de telefonía fija para la tarifa 147</t>
+        </is>
+      </c>
       <c r="AC52" s="21">
         <f>IF(C52="","",(Q52="Sí")+(S52="Sí")+(U52="Sí")+(W52="Sí")+(Y52="Sí")+(AA52="Sí"))</f>
         <v/>
       </c>
+      <c r="AD52" s="68" t="inlineStr">
+        <is>
+          <t>Registro definitivo</t>
+        </is>
+      </c>
+      <c r="AE52" s="2" t="inlineStr">
+        <is>
+          <t>26850</t>
+        </is>
+      </c>
+      <c r="AF52" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20 14:07:46</t>
+        </is>
+      </c>
+      <c r="AG52" s="2" t="inlineStr">
+        <is>
+          <t>duración 365 días | registro definitivo OK</t>
+        </is>
+      </c>
     </row>
     <row r="53">
+      <c r="A53" t="n">
+        <v>48</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>TL-LYC-CM-148</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
       <c r="E53" s="23" t="n"/>
+      <c r="F53" t="n">
+        <v>365</v>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>CTR-CM-148</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>2547.00</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>Euro</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>20100000148</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>Empresa contratante de prueba 148 SAC</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>Servicio licitado de prueba (AC+OS+TVP+IF+SM+TF)</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>Atributos de la tarifa de prueba 148</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>Lima Metropolitana</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>Detalle de arrendamiento de circuitos para la tarifa 148</t>
+        </is>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Detalle de otros servicios para la tarifa 148</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Detalle de televisión de paga para la tarifa 148</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>Detalle de internet fijo para la tarifa 148</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>Detalle de servicio móvil para la tarifa 148</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>Detalle de telefonía fija para la tarifa 148</t>
+        </is>
+      </c>
       <c r="AC53" s="21">
         <f>IF(C53="","",(Q53="Sí")+(S53="Sí")+(U53="Sí")+(W53="Sí")+(Y53="Sí")+(AA53="Sí"))</f>
         <v/>
+      </c>
+      <c r="AD53" s="68" t="inlineStr">
+        <is>
+          <t>Registro definitivo</t>
+        </is>
+      </c>
+      <c r="AE53" s="2" t="inlineStr">
+        <is>
+          <t>26851</t>
+        </is>
+      </c>
+      <c r="AF53" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20 14:08:00</t>
+        </is>
+      </c>
+      <c r="AG53" s="2" t="inlineStr">
+        <is>
+          <t>duración 365 días | registro definitivo OK</t>
+        </is>
       </c>
     </row>
     <row r="54">
